--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8590E5F7-F537-462B-9C79-43EEAA244341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BD7FFE3-23A2-4D7A-A7CB-4DEC513A2D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -1287,13 +1287,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S4aH2,S3aH2,S1aH2</t>
+    <t>S2aH2,S1aH2,S3aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S3aH3,S4aH1,S2aH1,S3aH1,S1aH1,S4aH3,S1aH3</t>
+    <t>S3aH3,S4aH1,S1aH3,S2aH3,S2aH1,S1aH1,S4aH3,S3aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S3aH3,S4aH1,S2aH1,S3aH1,S1aH1,S4aH3,S1aH3</v>
+        <v>S3aH3,S4aH1,S1aH3,S2aH3,S2aH1,S1aH1,S4aH3,S3aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S4aH2,S3aH2,S1aH2</v>
+        <v>S2aH2,S1aH2,S3aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2016,7 +2016,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F137E74-6F50-414F-9627-9296F5C22213}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EACF290-D7C9-49EC-932D-D68C31F6183D}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2100,7 +2100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4541965-2E96-4D54-A492-AA02DEB0FCA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{356866BE-7725-4141-8D6C-5E7B07CA5325}">
   <dimension ref="B9:O946"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -28370,7 +28370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61E5010B-6088-44E1-934B-7893752D77C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC9CB40-762E-471E-AB5B-7F8CE199C64C}">
   <dimension ref="B9:BL179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -44888,7 +44888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A527F3B6-DDCF-4972-8790-01F1A1D97C23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4AC243-A25B-4413-87F4-BE0E4347485B}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -45078,7 +45078,7 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.56168582465078831</v>
+        <v>0.56168582465078842</v>
       </c>
       <c r="S13" t="s">
         <v>424</v>
@@ -45242,7 +45242,7 @@
         <v>43</v>
       </c>
       <c r="R17">
-        <v>0.56513738013620773</v>
+        <v>0.56513738013620785</v>
       </c>
       <c r="S17" t="s">
         <v>424</v>
@@ -45447,7 +45447,7 @@
         <v>45</v>
       </c>
       <c r="R22">
-        <v>0.50361319976095009</v>
+        <v>0.5036131997609502</v>
       </c>
       <c r="S22" t="s">
         <v>424</v>
@@ -45587,7 +45587,7 @@
         <v>43</v>
       </c>
       <c r="R29">
-        <v>0.61353333333333337</v>
+        <v>0.61353333333333326</v>
       </c>
       <c r="S29" t="s">
         <v>424</v>
@@ -45729,7 +45729,7 @@
         <v>43</v>
       </c>
       <c r="R37">
-        <v>0.56366666666666665</v>
+        <v>0.56366666666666676</v>
       </c>
       <c r="S37" t="s">
         <v>424</v>
@@ -45841,7 +45841,7 @@
         <v>43</v>
       </c>
       <c r="R45">
-        <v>0.55986666666666673</v>
+        <v>0.55986666666666662</v>
       </c>
       <c r="S45" t="s">
         <v>424</v>
@@ -46023,7 +46023,7 @@
         <v>45</v>
       </c>
       <c r="R58">
-        <v>0.44933333333333331</v>
+        <v>0.44933333333333336</v>
       </c>
       <c r="S58" t="s">
         <v>424</v>
@@ -46121,7 +46121,7 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.54843333333333333</v>
+        <v>0.54843333333333322</v>
       </c>
       <c r="S65" t="s">
         <v>424</v>
@@ -46177,7 +46177,7 @@
         <v>43</v>
       </c>
       <c r="R69">
-        <v>0.55680000000000007</v>
+        <v>0.55679999999999996</v>
       </c>
       <c r="S69" t="s">
         <v>424</v>
@@ -46233,7 +46233,7 @@
         <v>43</v>
       </c>
       <c r="R73">
-        <v>0.5447333333333334</v>
+        <v>0.54473333333333329</v>
       </c>
       <c r="S73" t="s">
         <v>424</v>
@@ -46401,7 +46401,7 @@
         <v>43</v>
       </c>
       <c r="R85">
-        <v>0.55886666666666662</v>
+        <v>0.55886666666666673</v>
       </c>
       <c r="S85" t="s">
         <v>424</v>
@@ -46457,7 +46457,7 @@
         <v>43</v>
       </c>
       <c r="R89">
-        <v>0.46699999999999992</v>
+        <v>0.46700000000000003</v>
       </c>
       <c r="S89" t="s">
         <v>424</v>
@@ -46569,7 +46569,7 @@
         <v>43</v>
       </c>
       <c r="R97">
-        <v>0.47156666666666663</v>
+        <v>0.47156666666666669</v>
       </c>
       <c r="S97" t="s">
         <v>424</v>
@@ -46583,7 +46583,7 @@
         <v>45</v>
       </c>
       <c r="R98">
-        <v>0.39066666666666666</v>
+        <v>0.39066666666666672</v>
       </c>
       <c r="S98" t="s">
         <v>424</v>
@@ -46639,7 +46639,7 @@
         <v>45</v>
       </c>
       <c r="R102">
-        <v>0.37180000000000007</v>
+        <v>0.37179999999999996</v>
       </c>
       <c r="S102" t="s">
         <v>424</v>
@@ -46793,7 +46793,7 @@
         <v>43</v>
       </c>
       <c r="R113">
-        <v>0.54623333333333324</v>
+        <v>0.54623333333333335</v>
       </c>
       <c r="S113" t="s">
         <v>424</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BD7FFE3-23A2-4D7A-A7CB-4DEC513A2D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDE56B4-376E-4D25-B544-762D239078D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -19,9 +19,6 @@
     <sheet name="firmness" sheetId="9" r:id="rId4"/>
     <sheet name="load_demand_peak_hydro" sheetId="10" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7588" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7589" uniqueCount="425">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -1287,13 +1284,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S1aH2,S3aH2,S4aH2</t>
+    <t>S2aH2,S3aH2,S1aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH3,S4aH1,S1aH3,S2aH3,S2aH1,S1aH1,S4aH3,S3aH1</t>
+    <t>S3aH3,S4aH1,S2aH3,S1aH1,S4aH3,S1aH3,S3aH1,S2aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1454,19 +1451,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Veda"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1790,9 +1774,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <f>IFERROR([1]Veda!D5,"ts_12")</f>
-        <v>ts_12</v>
+      <c r="A10" t="s">
+        <v>46</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
@@ -1888,7 +1871,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH3,S4aH1,S1aH3,S2aH3,S2aH1,S1aH1,S4aH3,S3aH1</v>
+        <v>S3aH3,S4aH1,S2aH3,S1aH1,S4aH3,S1aH3,S3aH1,S2aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1920,7 +1903,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S1aH2,S3aH2,S4aH2</v>
+        <v>S2aH2,S3aH2,S1aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2016,7 +1999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EACF290-D7C9-49EC-932D-D68C31F6183D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD879F1F-8CD9-4541-9302-FC48B0EE1B9F}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2047,10 +2030,6 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11" t="s">
         <v>37</v>
       </c>
@@ -2100,7 +2079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{356866BE-7725-4141-8D6C-5E7B07CA5325}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70FA3E28-1F71-4515-B91D-B155A611A4D7}">
   <dimension ref="B9:O946"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -28370,7 +28349,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC9CB40-762E-471E-AB5B-7F8CE199C64C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A03289-3B48-427A-881E-CE5AA05A62DF}">
   <dimension ref="B9:BL179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -44888,7 +44867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4AC243-A25B-4413-87F4-BE0E4347485B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24029E03-B671-416B-87C0-53B061355D57}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -44958,10 +44937,6 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11">
         <v>8.2191780821917804E-2</v>
       </c>
@@ -44996,7 +44971,7 @@
         <v>37</v>
       </c>
       <c r="R11">
-        <v>0.26990853121428832</v>
+        <v>0.26990853121428826</v>
       </c>
       <c r="S11" t="s">
         <v>424</v>
@@ -45078,7 +45053,7 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.56168582465078842</v>
+        <v>0.56168582465078831</v>
       </c>
       <c r="S13" t="s">
         <v>424</v>
@@ -45242,7 +45217,7 @@
         <v>43</v>
       </c>
       <c r="R17">
-        <v>0.56513738013620785</v>
+        <v>0.56513738013620773</v>
       </c>
       <c r="S17" t="s">
         <v>424</v>
@@ -45447,7 +45422,7 @@
         <v>45</v>
       </c>
       <c r="R22">
-        <v>0.5036131997609502</v>
+        <v>0.50361319976095009</v>
       </c>
       <c r="S22" t="s">
         <v>424</v>
@@ -45527,7 +45502,7 @@
         <v>45</v>
       </c>
       <c r="R26">
-        <v>0.55593333333333328</v>
+        <v>0.55593333333333339</v>
       </c>
       <c r="S26" t="s">
         <v>424</v>
@@ -45587,7 +45562,7 @@
         <v>43</v>
       </c>
       <c r="R29">
-        <v>0.61353333333333326</v>
+        <v>0.61353333333333337</v>
       </c>
       <c r="S29" t="s">
         <v>424</v>
@@ -45701,7 +45676,7 @@
         <v>37</v>
       </c>
       <c r="R35">
-        <v>0.24966666666666668</v>
+        <v>0.2496666666666667</v>
       </c>
       <c r="S35" t="s">
         <v>424</v>
@@ -45715,7 +45690,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.32713333333333333</v>
+        <v>0.32713333333333328</v>
       </c>
       <c r="S36" t="s">
         <v>424</v>
@@ -45729,7 +45704,7 @@
         <v>43</v>
       </c>
       <c r="R37">
-        <v>0.56366666666666676</v>
+        <v>0.56366666666666665</v>
       </c>
       <c r="S37" t="s">
         <v>424</v>
@@ -45939,7 +45914,7 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.32830000000000004</v>
+        <v>0.32829999999999998</v>
       </c>
       <c r="S52" t="s">
         <v>424</v>
@@ -45967,7 +45942,7 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.42126666666666668</v>
+        <v>0.42126666666666662</v>
       </c>
       <c r="S54" t="s">
         <v>424</v>
@@ -46023,7 +45998,7 @@
         <v>45</v>
       </c>
       <c r="R58">
-        <v>0.44933333333333336</v>
+        <v>0.44933333333333331</v>
       </c>
       <c r="S58" t="s">
         <v>424</v>
@@ -46079,7 +46054,7 @@
         <v>45</v>
       </c>
       <c r="R62">
-        <v>0.43849999999999995</v>
+        <v>0.43850000000000006</v>
       </c>
       <c r="S62" t="s">
         <v>424</v>
@@ -46093,7 +46068,7 @@
         <v>37</v>
       </c>
       <c r="R63">
-        <v>0.25706666666666672</v>
+        <v>0.25706666666666667</v>
       </c>
       <c r="S63" t="s">
         <v>424</v>
@@ -46121,7 +46096,7 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.54843333333333322</v>
+        <v>0.54843333333333333</v>
       </c>
       <c r="S65" t="s">
         <v>424</v>
@@ -46135,7 +46110,7 @@
         <v>45</v>
       </c>
       <c r="R66">
-        <v>0.435</v>
+        <v>0.43500000000000005</v>
       </c>
       <c r="S66" t="s">
         <v>424</v>
@@ -46191,7 +46166,7 @@
         <v>45</v>
       </c>
       <c r="R70">
-        <v>0.43786666666666668</v>
+        <v>0.43786666666666663</v>
       </c>
       <c r="S70" t="s">
         <v>424</v>
@@ -46331,7 +46306,7 @@
         <v>41</v>
       </c>
       <c r="R80">
-        <v>0.32556666666666673</v>
+        <v>0.32556666666666667</v>
       </c>
       <c r="S80" t="s">
         <v>424</v>
@@ -46401,7 +46376,7 @@
         <v>43</v>
       </c>
       <c r="R85">
-        <v>0.55886666666666673</v>
+        <v>0.55886666666666651</v>
       </c>
       <c r="S85" t="s">
         <v>424</v>
@@ -46443,7 +46418,7 @@
         <v>41</v>
       </c>
       <c r="R88">
-        <v>0.2752</v>
+        <v>0.27519999999999994</v>
       </c>
       <c r="S88" t="s">
         <v>424</v>
@@ -46569,7 +46544,7 @@
         <v>43</v>
       </c>
       <c r="R97">
-        <v>0.47156666666666669</v>
+        <v>0.47156666666666663</v>
       </c>
       <c r="S97" t="s">
         <v>424</v>
@@ -46583,7 +46558,7 @@
         <v>45</v>
       </c>
       <c r="R98">
-        <v>0.39066666666666672</v>
+        <v>0.39066666666666666</v>
       </c>
       <c r="S98" t="s">
         <v>424</v>
@@ -46821,7 +46796,7 @@
         <v>37</v>
       </c>
       <c r="R115">
-        <v>0.24033333333333332</v>
+        <v>0.24033333333333337</v>
       </c>
       <c r="S115" t="s">
         <v>424</v>
@@ -46835,7 +46810,7 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.33780000000000004</v>
+        <v>0.33779999999999993</v>
       </c>
       <c r="S116" t="s">
         <v>424</v>
@@ -46863,7 +46838,7 @@
         <v>45</v>
       </c>
       <c r="R118">
-        <v>0.44803333333333334</v>
+        <v>0.44803333333333328</v>
       </c>
       <c r="S118" t="s">
         <v>424</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDE56B4-376E-4D25-B544-762D239078D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A4572C-ADDA-4DAB-A7A6-BB3E6D324B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1284,13 +1284,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S3aH2,S1aH2,S4aH2</t>
+    <t>S4aH2,S1aH2,S2aH2,S3aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH3,S4aH1,S2aH3,S1aH1,S4aH3,S1aH3,S3aH1,S2aH1</t>
+    <t>S2aH3,S1aH1,S4aH3,S2aH1,S3aH1,S1aH3,S3aH3,S4aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH3,S4aH1,S2aH3,S1aH1,S4aH3,S1aH3,S3aH1,S2aH1</v>
+        <v>S2aH3,S1aH1,S4aH3,S2aH1,S3aH1,S1aH3,S3aH3,S4aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S3aH2,S1aH2,S4aH2</v>
+        <v>S4aH2,S1aH2,S2aH2,S3aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1999,7 +1999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD879F1F-8CD9-4541-9302-FC48B0EE1B9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75C83BE-0DF2-476C-A3DC-DD0135821297}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2079,7 +2079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70FA3E28-1F71-4515-B91D-B155A611A4D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88CCBD9F-D1A4-4CF4-B0A4-E8566CDDE6FB}">
   <dimension ref="B9:O946"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -28349,7 +28349,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A03289-3B48-427A-881E-CE5AA05A62DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12F3B2E-E72D-465F-9FA1-9AD93CF7D77D}">
   <dimension ref="B9:BL179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -44867,7 +44867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24029E03-B671-416B-87C0-53B061355D57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ADC3CCD-402A-4D11-A33C-733EED161E8B}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -44971,7 +44971,7 @@
         <v>37</v>
       </c>
       <c r="R11">
-        <v>0.26990853121428826</v>
+        <v>0.26990853121428832</v>
       </c>
       <c r="S11" t="s">
         <v>424</v>
@@ -45053,7 +45053,7 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.56168582465078831</v>
+        <v>0.56168582465078842</v>
       </c>
       <c r="S13" t="s">
         <v>424</v>
@@ -45217,7 +45217,7 @@
         <v>43</v>
       </c>
       <c r="R17">
-        <v>0.56513738013620773</v>
+        <v>0.56513738013620785</v>
       </c>
       <c r="S17" t="s">
         <v>424</v>
@@ -45562,7 +45562,7 @@
         <v>43</v>
       </c>
       <c r="R29">
-        <v>0.61353333333333337</v>
+        <v>0.61353333333333326</v>
       </c>
       <c r="S29" t="s">
         <v>424</v>
@@ -45676,7 +45676,7 @@
         <v>37</v>
       </c>
       <c r="R35">
-        <v>0.2496666666666667</v>
+        <v>0.24966666666666668</v>
       </c>
       <c r="S35" t="s">
         <v>424</v>
@@ -45704,7 +45704,7 @@
         <v>43</v>
       </c>
       <c r="R37">
-        <v>0.56366666666666665</v>
+        <v>0.56366666666666676</v>
       </c>
       <c r="S37" t="s">
         <v>424</v>
@@ -46068,7 +46068,7 @@
         <v>37</v>
       </c>
       <c r="R63">
-        <v>0.25706666666666667</v>
+        <v>0.25706666666666672</v>
       </c>
       <c r="S63" t="s">
         <v>424</v>
@@ -46096,7 +46096,7 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.54843333333333333</v>
+        <v>0.54843333333333322</v>
       </c>
       <c r="S65" t="s">
         <v>424</v>
@@ -46376,7 +46376,7 @@
         <v>43</v>
       </c>
       <c r="R85">
-        <v>0.55886666666666651</v>
+        <v>0.55886666666666673</v>
       </c>
       <c r="S85" t="s">
         <v>424</v>
@@ -46544,7 +46544,7 @@
         <v>43</v>
       </c>
       <c r="R97">
-        <v>0.47156666666666663</v>
+        <v>0.47156666666666669</v>
       </c>
       <c r="S97" t="s">
         <v>424</v>
@@ -46796,7 +46796,7 @@
         <v>37</v>
       </c>
       <c r="R115">
-        <v>0.24033333333333337</v>
+        <v>0.24033333333333332</v>
       </c>
       <c r="S115" t="s">
         <v>424</v>
